--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487523_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487523_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3469</v>
+        <v>12.1691</v>
       </c>
       <c r="E2" t="n">
-        <v>12.5011</v>
+        <v>11.5371</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8459</v>
+        <v>0.632</v>
       </c>
       <c r="G2" t="n">
         <v>8.2006</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1451</v>
+        <v>1.9673</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5378</v>
+        <v>1.5738</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6073</v>
+        <v>0.3935</v>
       </c>
       <c r="V2" t="n">
         <v>0.8260999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>M. SOUTO PARRADO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>10.4499</v>
+        <v>9.1371</v>
       </c>
       <c r="E3" t="n">
-        <v>8.191700000000001</v>
+        <v>7.5214</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2582</v>
+        <v>1.6156</v>
       </c>
       <c r="G3" t="n">
-        <v>5.4575</v>
+        <v>3.1955</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2903</v>
+        <v>0.5685</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1672</v>
+        <v>2.627</v>
       </c>
       <c r="J3" t="n">
-        <v>6.9314</v>
+        <v>4.8007</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5121</v>
+        <v>1.5174</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4193</v>
+        <v>3.2833</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4739</v>
+        <v>-1.6052</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2218</v>
+        <v>-0.9489</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2521</v>
+        <v>-0.6563</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>2.9377</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1336</v>
+        <v>2.9377</v>
       </c>
       <c r="S3" t="n">
-        <v>4.7585</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8846</v>
+        <v>0.6781</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8739</v>
+        <v>0.283</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9412</v>
+        <v>2.0427</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6659</v>
+        <v>2.0427</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. SOUTO PARRADO</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8.6859</v>
+        <v>8.0708</v>
       </c>
       <c r="E4" t="n">
-        <v>7.2574</v>
+        <v>5.9997</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4285</v>
+        <v>2.0711</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1955</v>
+        <v>5.4575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5685</v>
+        <v>4.2903</v>
       </c>
       <c r="I4" t="n">
-        <v>2.627</v>
+        <v>1.1672</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8007</v>
+        <v>6.9314</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5174</v>
+        <v>5.5121</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2833</v>
+        <v>1.4193</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6052</v>
+        <v>-1.4739</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9489</v>
+        <v>-1.2218</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6563</v>
+        <v>-0.2521</v>
       </c>
       <c r="P4" t="n">
-        <v>2.9377</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9377</v>
+        <v>3.1336</v>
       </c>
       <c r="S4" t="n">
-        <v>0.51</v>
+        <v>2.3794</v>
       </c>
       <c r="T4" t="n">
-        <v>0.414</v>
+        <v>1.6926</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0959</v>
+        <v>0.6868</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0427</v>
+        <v>-0.9412</v>
       </c>
       <c r="W4" t="n">
-        <v>2.0427</v>
+        <v>-0.6659</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.0095</v>
+        <v>4.5398</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2723</v>
+        <v>2.6115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7372</v>
+        <v>1.9283</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2015</v>
+        <v>-0.2569</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5189</v>
+        <v>-0.7522</v>
       </c>
       <c r="I5" t="n">
-        <v>2.6826</v>
+        <v>0.4954</v>
       </c>
       <c r="J5" t="n">
-        <v>2.587</v>
+        <v>-0.0058</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0408</v>
+        <v>-0.2127</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5462</v>
+        <v>0.2069</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6145</v>
+        <v>-0.2511</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4781</v>
+        <v>-0.5395</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1364</v>
+        <v>0.2885</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3917</v>
+        <v>2.1543</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0833</v>
+        <v>0.2091</v>
       </c>
       <c r="T5" t="n">
-        <v>0.077</v>
+        <v>0.1841</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0063</v>
+        <v>0.025</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3329</v>
+        <v>2.4332</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6083</v>
+        <v>2.4332</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.9746</v>
+        <v>4.0851</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0998</v>
+        <v>3.3747</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8748</v>
+        <v>0.7104</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2569</v>
+        <v>3.2015</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7522</v>
+        <v>0.5189</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4954</v>
+        <v>2.6826</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0058</v>
+        <v>2.587</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2127</v>
+        <v>0.0408</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2069</v>
+        <v>2.5462</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2511</v>
+        <v>0.6145</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5395</v>
+        <v>0.4781</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2885</v>
+        <v>0.1364</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1543</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1543</v>
+        <v>0.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3561</v>
+        <v>0.1589</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3276</v>
+        <v>0.1794</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0285</v>
+        <v>-0.0204</v>
       </c>
       <c r="V6" t="n">
-        <v>2.4332</v>
+        <v>0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4332</v>
+        <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9953</v>
+        <v>1.9197</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7419</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2534</v>
+        <v>1.2801</v>
       </c>
       <c r="G7" t="n">
         <v>1.2534</v>
@@ -1000,13 +1000,13 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3501</v>
+        <v>0.2745</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4446</v>
+        <v>0.3423</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0945</v>
+        <v>-0.0678</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ FRAIZ</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1728</v>
+        <v>0.4301</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3549</v>
+        <v>1.5332</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5277</v>
+        <v>-1.1031</v>
       </c>
       <c r="G8" t="n">
-        <v>2.963</v>
+        <v>0.4667</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4131</v>
+        <v>-0.2708</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.7375</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1809</v>
+        <v>1.1406</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3184</v>
+        <v>0.4083</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.1376</v>
+        <v>0.7323</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7821</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0947</v>
+        <v>-0.6791</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6874</v>
+        <v>0.0052</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3502</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5668</v>
+        <v>0.9792</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0519</v>
+        <v>0.2388</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1059</v>
+        <v>0.1553</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.0835</v>
       </c>
       <c r="V8" t="n">
+        <v>-0.2754</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="X8" t="n">
         <v>-1.492</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-1.7673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>J. DOMINGUEZ FRAIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2954</v>
+        <v>-0.2687</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0215</v>
+        <v>-2.0479</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.317</v>
+        <v>1.7792</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4667</v>
+        <v>2.963</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2708</v>
+        <v>2.4131</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7375</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1406</v>
+        <v>1.1809</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4083</v>
+        <v>1.3184</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7323</v>
+        <v>-0.1376</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6739000000000001</v>
+        <v>1.7821</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6791</v>
+        <v>1.0947</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0052</v>
+        <v>0.6874</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9792</v>
+        <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4867</v>
+        <v>0.6105</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>0.4129</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1303</v>
+        <v>0.1976</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2166</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.492</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.2057</v>
+        <v>-2.4046</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1148</v>
+        <v>-2.5008</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.091</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-0.604</v>
@@ -1234,13 +1234,13 @@
         <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5222</v>
+        <v>0.2789</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3982</v>
+        <v>0.2158</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.124</v>
+        <v>0.0631</v>
       </c>
       <c r="V10" t="n">
         <v>-1.492</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. PAZ CACHEIRO</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5674</v>
+        <v>-2.5624</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.089</v>
+        <v>-5.4581</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5216</v>
+        <v>2.8957</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5165</v>
+        <v>-4.5385</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8094</v>
+        <v>-1.7128</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2929</v>
+        <v>-2.8257</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2779</v>
+        <v>-3.8125</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.8834</v>
+        <v>-0.4254</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3945</v>
+        <v>-3.3871</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7614</v>
+        <v>-0.726</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07389999999999999</v>
+        <v>-1.2874</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6874</v>
+        <v>0.5614</v>
       </c>
       <c r="P11" t="n">
+        <v>1.5668</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-1.9585</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.9585</v>
+        <v>3.5253</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2076</v>
+        <v>0.4093</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1059</v>
+        <v>0.3129</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3134</v>
+        <v>0.0965</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>M. PAZ CACHEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7612</v>
+        <v>-3.0139</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.3362</v>
+        <v>-5.7226</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5749</v>
+        <v>2.7087</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.5385</v>
+        <v>-1.5165</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.7128</v>
+        <v>-1.8094</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.8257</v>
+        <v>0.2929</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.8125</v>
+        <v>-2.2779</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4254</v>
+        <v>-1.8834</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3871</v>
+        <v>-0.3945</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.726</v>
+        <v>0.7614</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2874</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5614</v>
+        <v>0.6874</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5668</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R12" t="n">
-        <v>3.5253</v>
+        <v>1.9585</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7895</v>
+        <v>0.346</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5652</v>
+        <v>0.4723</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2243</v>
+        <v>-0.1263</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.8052</v>
+        <v>32.1021</v>
       </c>
       <c r="E13" t="n">
-        <v>17.1908</v>
+        <v>17.4878</v>
       </c>
       <c r="F13" t="n">
         <v>14.6142</v>
@@ -1459,7 +1459,7 @@
         <v>1.4942</v>
       </c>
       <c r="P13" t="n">
-        <v>4.8962</v>
+        <v>4.896199999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-16.6472</v>
@@ -1468,16 +1468,16 @@
         <v>21.5433</v>
       </c>
       <c r="S13" t="n">
-        <v>7.536799999999999</v>
+        <v>7.8339</v>
       </c>
       <c r="T13" t="n">
-        <v>5.9224</v>
+        <v>6.2195</v>
       </c>
       <c r="U13" t="n">
         <v>1.6145</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5495</v>
+        <v>1.549499999999999</v>
       </c>
       <c r="W13" t="n">
         <v>8.228299999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4766</v>
+        <v>1.1662</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2205</v>
+        <v>4.9369</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7439</v>
+        <v>-3.7706</v>
       </c>
       <c r="G14" t="n">
         <v>2.4616</v>
@@ -1546,13 +1546,13 @@
         <v>1.5668</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8687</v>
+        <v>-1.1791</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.188</v>
+        <v>-0.4717</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6806</v>
+        <v>-0.7074</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2254</v>
+        <v>0.6439</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.0979</v>
+        <v>-1.8933</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3234</v>
+        <v>2.5372</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7195</v>
@@ -1624,13 +1624,13 @@
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8961</v>
+        <v>-0.4776</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2682</v>
+        <v>-0.0635</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6279</v>
+        <v>-0.414</v>
       </c>
       <c r="V15" t="n">
         <v>0.6659</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1343</v>
+        <v>-0.3081</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2164</v>
+        <v>-0.0002</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.3079</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9952</v>
+        <v>-0.0867</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0916</v>
+        <v>0.2719</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0964</v>
+        <v>-0.3585</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2629</v>
+        <v>1.5216</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3437</v>
+        <v>0.951</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0808</v>
+        <v>0.5706</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7323</v>
+        <v>-1.6083</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7479</v>
+        <v>-0.6791</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0156</v>
+        <v>-0.9292</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R16" t="n">
         <v>1.3709</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6858</v>
+        <v>-0.4599</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0257</v>
+        <v>-0.3893</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6601</v>
+        <v>-0.0706</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2166</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6197</v>
+        <v>-1.2221</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2048</v>
+        <v>-0.9328</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4148</v>
+        <v>-0.2893</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0867</v>
+        <v>-0.9952</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2719</v>
+        <v>-1.0916</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3585</v>
+        <v>0.0964</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5216</v>
+        <v>-0.2629</v>
       </c>
       <c r="K17" t="n">
-        <v>0.951</v>
+        <v>-0.3437</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5706</v>
+        <v>0.0808</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6083</v>
+        <v>-0.7323</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6791</v>
+        <v>-0.7479</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9292</v>
+        <v>0.0156</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7715</v>
+        <v>0.598</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.594</v>
+        <v>0.3094</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1775</v>
+        <v>0.2886</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8260999999999999</v>
+        <v>-1.2166</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. FOLCH CLARAMUNT</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5657</v>
+        <v>-1.7907</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.512</v>
+        <v>-2.0394</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0537</v>
+        <v>0.2488</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0679</v>
+        <v>2.7931</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6189</v>
+        <v>0.62</v>
       </c>
       <c r="I18" t="n">
-        <v>0.551</v>
+        <v>2.1731</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0612</v>
+        <v>1.4193</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0612</v>
+        <v>1.298</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1212</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1292</v>
+        <v>1.3738</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6802</v>
+        <v>-0.6781</v>
       </c>
       <c r="O18" t="n">
-        <v>0.551</v>
+        <v>2.0519</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5668</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3444</v>
+        <v>-0.3499</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3852</v>
+        <v>0.1829</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0409</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2754</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>A. ESPIÑEIRA ANDRADE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6247</v>
+        <v>-1.9686</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6301</v>
+        <v>-0.4279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0054</v>
+        <v>-1.5407</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7931</v>
+        <v>-2.2872</v>
       </c>
       <c r="H19" t="n">
-        <v>0.62</v>
+        <v>-0.2664</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1731</v>
+        <v>-2.0208</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4193</v>
+        <v>-0.405</v>
       </c>
       <c r="K19" t="n">
-        <v>1.298</v>
+        <v>0.2773</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1212</v>
+        <v>-0.6822</v>
       </c>
       <c r="M19" t="n">
-        <v>1.3738</v>
+        <v>-1.8822</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6781</v>
+        <v>-0.5437</v>
       </c>
       <c r="O19" t="n">
-        <v>2.0519</v>
+        <v>-1.3385</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7419</v>
+        <v>0.9792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.184</v>
+        <v>-0.6606</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.0229</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7762</v>
+        <v>-0.6377</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ESPIÑEIRA ANDRADE</t>
+          <t>X. FOLCH CLARAMUNT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8247</v>
+        <v>-2.1087</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1209</v>
+        <v>-1.9214</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7038</v>
+        <v>-0.1874</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2872</v>
+        <v>-0.0679</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2664</v>
+        <v>-0.6189</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0208</v>
+        <v>0.551</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.405</v>
+        <v>0.0612</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2773</v>
+        <v>0.0612</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6822</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8822</v>
+        <v>-0.1292</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5437</v>
+        <v>-0.6802</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3385</v>
+        <v>0.551</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9792</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5168</v>
+        <v>-0.1986</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2841</v>
+        <v>-0.0241</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.1745</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6959</v>
+        <v>-2.9897</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6596</v>
+        <v>-0.2503</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0363</v>
+        <v>-2.7394</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2874</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2287</v>
+        <v>-0.5226</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.517</v>
+        <v>-0.1076</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7118</v>
+        <v>-0.4149</v>
       </c>
       <c r="V21" t="n">
         <v>-1.159</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2745</v>
+        <v>-4.3786</v>
       </c>
       <c r="E22" t="n">
         <v>-0.8501</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.4244</v>
+        <v>-3.5285</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7849</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5103</v>
+        <v>-0.6145</v>
       </c>
       <c r="T22" t="n">
         <v>-0.31</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2004</v>
+        <v>-0.3045</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9935</v>
+        <v>-4.3971</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8486</v>
+        <v>-0.4393</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1449</v>
+        <v>-3.9578</v>
       </c>
       <c r="G23" t="n">
         <v>-5.8822</v>
@@ -2248,13 +2248,13 @@
         <v>2.1543</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0537</v>
+        <v>-1.4573</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8734</v>
+        <v>-0.464</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1803</v>
+        <v>-0.9932</v>
       </c>
       <c r="V23" t="n">
         <v>1.7673</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7749</v>
+        <v>-6.5852</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1625</v>
+        <v>-4.2246</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6123</v>
+        <v>-2.3606</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5781</v>
+        <v>-4.388</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.7847</v>
+        <v>-1.2968</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7935</v>
+        <v>-3.0912</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1125</v>
+        <v>-0.9099</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8337</v>
+        <v>0.3333</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2788</v>
+        <v>-1.2432</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4656</v>
+        <v>-3.4781</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.951</v>
+        <v>-1.6301</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-1.848</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3502</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5668</v>
+        <v>1.9585</v>
       </c>
       <c r="S24" t="n">
-        <v>0.09470000000000001</v>
+        <v>-1.218</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5328000000000001</v>
+        <v>-0.377</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4382</v>
+        <v>-0.841</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9412</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.9992</v>
+        <v>-7.1842</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.5317</v>
+        <v>-6.5719</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4675</v>
+        <v>-0.6123</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.388</v>
+        <v>-3.5781</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2968</v>
+        <v>-1.7847</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0912</v>
+        <v>-1.7935</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9099</v>
+        <v>-2.1125</v>
       </c>
       <c r="K25" t="n">
-        <v>0.3333</v>
+        <v>-0.8337</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.2432</v>
+        <v>-1.2788</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.4781</v>
+        <v>-1.4656</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6301</v>
+        <v>-0.951</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.848</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9792</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9377</v>
+        <v>-3.917</v>
       </c>
       <c r="R25" t="n">
-        <v>1.9585</v>
+        <v>1.5668</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.632</v>
+        <v>-0.3147</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6840000000000001</v>
+        <v>0.1235</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.948</v>
+        <v>-0.4382</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.9412</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.8051</v>
+        <v>-31.1229</v>
       </c>
       <c r="E26" t="n">
-        <v>-14.6141</v>
+        <v>-14.6143</v>
       </c>
       <c r="F26" t="n">
-        <v>-17.1907</v>
+        <v>-16.5085</v>
       </c>
       <c r="G26" t="n">
         <v>-17.8224</v>
@@ -2452,7 +2452,7 @@
         <v>-7.8482</v>
       </c>
       <c r="I26" t="n">
-        <v>-9.9742</v>
+        <v>-9.974200000000002</v>
       </c>
       <c r="J26" t="n">
         <v>1.8649</v>
@@ -2473,7 +2473,7 @@
         <v>-8.479600000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.896199999999999</v>
+        <v>-4.8962</v>
       </c>
       <c r="Q26" t="n">
         <v>-21.5433</v>
@@ -2482,13 +2482,13 @@
         <v>16.647</v>
       </c>
       <c r="S26" t="n">
-        <v>-7.536899999999999</v>
+        <v>-6.854800000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6146</v>
+        <v>-1.6143</v>
       </c>
       <c r="U26" t="n">
-        <v>-5.922600000000001</v>
+        <v>-5.2402</v>
       </c>
       <c r="V26" t="n">
         <v>-1.5495</v>
